--- a/預測結果與評估指標_kfold_mask幾何_性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_性別.xlsx
@@ -427,7 +427,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.42578125" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>403.60700000000003</v>
+        <v>405.481</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.998906332136819</v>
+        <v>20.991328932879696</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.0010936678631808</v>
+        <v>-2.0086710671203036</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0010936678631808</v>
+        <v>2.0086710671203036</v>
       </c>
       <c r="H2" s="0">
-        <v>20.498906332136819</v>
+        <v>20.491328932879696</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.5010936678631808</v>
+        <v>-2.5086710671203036</v>
       </c>
       <c r="J2" s="0">
-        <v>2.5010936678631808</v>
+        <v>2.5086710671203036</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>605.36530000000005</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.187973700647035</v>
+        <v>21.239284774403441</v>
       </c>
       <c r="F3" s="0">
-        <v>0.187973700647035</v>
+        <v>0.23928477440344054</v>
       </c>
       <c r="G3" s="0">
-        <v>0.187973700647035</v>
+        <v>0.23928477440344054</v>
       </c>
       <c r="H3" s="0">
-        <v>20.687973700647035</v>
+        <v>20.739284774403441</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.312026299352965</v>
+        <v>-0.26071522559655946</v>
       </c>
       <c r="J3" s="0">
-        <v>0.312026299352965</v>
+        <v>0.26071522559655946</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>740.86210000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079500656645408</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4128913961230651</v>
+        <v>-2.4204993433545923</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4128913961230651</v>
+        <v>2.4204993433545923</v>
       </c>
       <c r="H4" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579500656645408</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9128913961230651</v>
+        <v>-2.9204993433545923</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9128913961230651</v>
+        <v>2.9204993433545923</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>580.86249999999996</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.998857327399953</v>
+        <v>20.989258421389117</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.0011426726000465237</v>
+        <v>-0.010741578610883096</v>
       </c>
       <c r="G5" s="0">
-        <v>0.0011426726000465237</v>
+        <v>0.010741578610883096</v>
       </c>
       <c r="H5" s="0">
-        <v>20.498857327399953</v>
+        <v>20.489258421389117</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.50114267260004652</v>
+        <v>-0.5107415786108831</v>
       </c>
       <c r="J5" s="0">
-        <v>0.50114267260004652</v>
+        <v>0.5107415786108831</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>620.73389999999995</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.189645551792836</v>
+        <v>21.239294687759465</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.31035444820716407</v>
+        <v>-0.26070531224053539</v>
       </c>
       <c r="G6" s="0">
-        <v>0.31035444820716407</v>
+        <v>0.26070531224053539</v>
       </c>
       <c r="H6" s="0">
-        <v>20.689645551792836</v>
+        <v>20.739294687759465</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.81035444820716407</v>
+        <v>-0.76070531224053539</v>
       </c>
       <c r="J6" s="0">
-        <v>0.81035444820716407</v>
+        <v>0.76070531224053539</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>711.67399999999998</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>20.998946957023129</v>
+        <v>20.989560229304299</v>
       </c>
       <c r="F7" s="0">
-        <v>-1.0010530429768707</v>
+        <v>-1.0104397706957009</v>
       </c>
       <c r="G7" s="0">
-        <v>1.0010530429768707</v>
+        <v>1.0104397706957009</v>
       </c>
       <c r="H7" s="0">
-        <v>20.498946957023129</v>
+        <v>20.489560229304299</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.5010530429768707</v>
+        <v>-1.5104397706957009</v>
       </c>
       <c r="J7" s="0">
-        <v>1.5010530429768707</v>
+        <v>1.5104397706957009</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>757.66719999999998</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.037071751777635</v>
+        <v>21.037548648307567</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9629282482223651</v>
+        <v>-3.9624513516924331</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9629282482223651</v>
+        <v>3.9624513516924331</v>
       </c>
       <c r="H8" s="0">
-        <v>20.537071751777635</v>
+        <v>20.537548648307567</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.4629282482223651</v>
+        <v>-4.4624513516924331</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4629282482223651</v>
+        <v>4.4624513516924331</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>400.07780000000002</v>
+        <v>390.43310000000002</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.354763820891044</v>
+        <v>21.241081580510237</v>
       </c>
       <c r="F9" s="0">
-        <v>0.85476382089104419</v>
+        <v>0.74108158051023665</v>
       </c>
       <c r="G9" s="0">
-        <v>0.85476382089104419</v>
+        <v>0.74108158051023665</v>
       </c>
       <c r="H9" s="0">
-        <v>20.854763820891044</v>
+        <v>20.741081580510237</v>
       </c>
       <c r="I9" s="0">
-        <v>0.35476382089104419</v>
+        <v>0.24108158051023665</v>
       </c>
       <c r="J9" s="0">
-        <v>0.35476382089104419</v>
+        <v>0.24108158051023665</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1283.9973</v>
+        <v>1263.4103</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.410809772665651</v>
+        <v>21.241643288133851</v>
       </c>
       <c r="F10" s="0">
-        <v>0.410809772665651</v>
+        <v>0.24164328813385083</v>
       </c>
       <c r="G10" s="0">
-        <v>0.410809772665651</v>
+        <v>0.24164328813385083</v>
       </c>
       <c r="H10" s="0">
-        <v>20.910809772665651</v>
+        <v>20.741643288133851</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.089190227334349004</v>
+        <v>-0.25835671186614917</v>
       </c>
       <c r="J10" s="0">
-        <v>0.089190227334349004</v>
+        <v>0.25835671186614917</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>317.95030000000003</v>
+        <v>319.74869999999999</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.998691792320979</v>
+        <v>20.988656491413686</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9986917923209795</v>
+        <v>2.9886564914136855</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9986917923209795</v>
+        <v>2.9886564914136855</v>
       </c>
       <c r="H11" s="0">
-        <v>20.498691792320979</v>
+        <v>20.488656491413686</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4986917923209795</v>
+        <v>2.4886564914136855</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4986917923209795</v>
+        <v>2.4886564914136855</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>718.36379999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.947611213467514</v>
+        <v>20.850408337144373</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.0523887865324859</v>
+        <v>-4.1495916628556273</v>
       </c>
       <c r="G12" s="0">
-        <v>4.0523887865324859</v>
+        <v>4.1495916628556273</v>
       </c>
       <c r="H12" s="0">
-        <v>20.447611213467514</v>
+        <v>20.350408337144373</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.5523887865324859</v>
+        <v>-4.6495916628556273</v>
       </c>
       <c r="J12" s="0">
-        <v>4.5523887865324859</v>
+        <v>4.6495916628556273</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>669.91160000000002</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.947609683316692</v>
+        <v>20.851257230981329</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.552390316683308</v>
+        <v>-1.6487427690186713</v>
       </c>
       <c r="G13" s="0">
-        <v>1.552390316683308</v>
+        <v>1.6487427690186713</v>
       </c>
       <c r="H13" s="0">
-        <v>20.447609683316692</v>
+        <v>20.351257230981329</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.052390316683308</v>
+        <v>-2.1487427690186713</v>
       </c>
       <c r="J13" s="0">
-        <v>2.052390316683308</v>
+        <v>2.1487427690186713</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>672.01459999999997</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079499948536338</v>
       </c>
       <c r="F14" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949994853633768</v>
       </c>
       <c r="G14" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949994853633768</v>
       </c>
       <c r="H14" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579499948536338</v>
       </c>
       <c r="I14" s="0">
-        <v>0.087108603876934865</v>
+        <v>0.079499948536337684</v>
       </c>
       <c r="J14" s="0">
-        <v>0.087108603876934865</v>
+        <v>0.079499948536337684</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>585.0598</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>20.947063978552709</v>
+        <v>21.02962465008904</v>
       </c>
       <c r="F15" s="0">
-        <v>1.4470639785527091</v>
+        <v>1.5296246500890405</v>
       </c>
       <c r="G15" s="0">
-        <v>1.4470639785527091</v>
+        <v>1.5296246500890405</v>
       </c>
       <c r="H15" s="0">
-        <v>20.447063978552709</v>
+        <v>20.52962465008904</v>
       </c>
       <c r="I15" s="0">
-        <v>0.94706397855270907</v>
+        <v>1.0296246500890405</v>
       </c>
       <c r="J15" s="0">
-        <v>0.94706397855270907</v>
+        <v>1.0296246500890405</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.17600000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.368573322223977</v>
+        <v>21.241227996414743</v>
       </c>
       <c r="F16" s="0">
-        <v>1.8685733222239769</v>
+        <v>1.741227996414743</v>
       </c>
       <c r="G16" s="0">
-        <v>1.8685733222239769</v>
+        <v>1.741227996414743</v>
       </c>
       <c r="H16" s="0">
-        <v>20.868573322223977</v>
+        <v>20.741227996414743</v>
       </c>
       <c r="I16" s="0">
-        <v>1.3685733222239769</v>
+        <v>1.241227996414743</v>
       </c>
       <c r="J16" s="0">
-        <v>1.3685733222239769</v>
+        <v>1.241227996414743</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1130.2846</v>
+        <v>1122.4987000000001</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079504581848052</v>
       </c>
       <c r="F17" s="0">
-        <v>2.5871086038769349</v>
+        <v>2.5795045818480524</v>
       </c>
       <c r="G17" s="0">
-        <v>2.5871086038769349</v>
+        <v>2.5795045818480524</v>
       </c>
       <c r="H17" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579504581848052</v>
       </c>
       <c r="I17" s="0">
-        <v>2.0871086038769349</v>
+        <v>2.0795045818480524</v>
       </c>
       <c r="J17" s="0">
-        <v>2.0871086038769349</v>
+        <v>2.0795045818480524</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1452.2846</v>
+        <v>1459.4197999999999</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.9476255677761</v>
+        <v>20.837451851802516</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.8023744322238997</v>
+        <v>-2.9125481481974838</v>
       </c>
       <c r="G18" s="0">
-        <v>2.8023744322238997</v>
+        <v>2.9125481481974838</v>
       </c>
       <c r="H18" s="0">
-        <v>20.4476255677761</v>
+        <v>20.337451851802516</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.3023744322238997</v>
+        <v>-3.4125481481974838</v>
       </c>
       <c r="J18" s="0">
-        <v>3.3023744322238997</v>
+        <v>3.4125481481974838</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>667.94280000000003</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.037071751777635</v>
+        <v>21.03476410060512</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2129282482223651</v>
+        <v>-1.2152358993948802</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2129282482223651</v>
+        <v>1.2152358993948802</v>
       </c>
       <c r="H19" s="0">
-        <v>20.537071751777635</v>
+        <v>20.53476410060512</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7129282482223651</v>
+        <v>-1.7152358993948802</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7129282482223651</v>
+        <v>1.7152358993948802</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>755.404</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>20.999125862635339</v>
+        <v>20.992137599187867</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.5008741373646615</v>
+        <v>-4.5078624008121331</v>
       </c>
       <c r="G20" s="0">
-        <v>4.5008741373646615</v>
+        <v>4.5078624008121331</v>
       </c>
       <c r="H20" s="0">
-        <v>20.499125862635339</v>
+        <v>20.492137599187867</v>
       </c>
       <c r="I20" s="0">
-        <v>-5.0008741373646615</v>
+        <v>-5.0078624008121331</v>
       </c>
       <c r="J20" s="0">
-        <v>5.0008741373646615</v>
+        <v>5.0078624008121331</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>345.22919999999999</v>
+        <v>344.29160000000002</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.947602936572512</v>
+        <v>20.85696743230228</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.5523970634274882</v>
+        <v>-1.6430325676977198</v>
       </c>
       <c r="G21" s="0">
-        <v>1.5523970634274882</v>
+        <v>1.6430325676977198</v>
       </c>
       <c r="H21" s="0">
-        <v>20.447602936572512</v>
+        <v>20.35696743230228</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.0523970634274882</v>
+        <v>-2.1430325676977198</v>
       </c>
       <c r="J21" s="0">
-        <v>2.0523970634274882</v>
+        <v>2.1430325676977198</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>613.17560000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079499343366564</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.41289139612306514</v>
+        <v>-0.42050065663343617</v>
       </c>
       <c r="G22" s="0">
-        <v>0.41289139612306514</v>
+        <v>0.42050065663343617</v>
       </c>
       <c r="H22" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579499343366564</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.91289139612306514</v>
+        <v>-0.92050065663343617</v>
       </c>
       <c r="J22" s="0">
-        <v>0.91289139612306514</v>
+        <v>0.92050065663343617</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>674.47910000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079491003442506</v>
       </c>
       <c r="F23" s="0">
-        <v>1.0871086038769349</v>
+        <v>1.0794910034425058</v>
       </c>
       <c r="G23" s="0">
-        <v>1.0871086038769349</v>
+        <v>1.0794910034425058</v>
       </c>
       <c r="H23" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579491003442506</v>
       </c>
       <c r="I23" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949100344250582</v>
       </c>
       <c r="J23" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949100344250582</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>577.67240000000004</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.186542516844767</v>
+        <v>21.239266909717159</v>
       </c>
       <c r="F24" s="0">
-        <v>1.6865425168447672</v>
+        <v>1.7392669097171591</v>
       </c>
       <c r="G24" s="0">
-        <v>1.6865425168447672</v>
+        <v>1.7392669097171591</v>
       </c>
       <c r="H24" s="0">
-        <v>20.686542516844767</v>
+        <v>20.739266909717159</v>
       </c>
       <c r="I24" s="0">
-        <v>1.1865425168447672</v>
+        <v>1.2392669097171591</v>
       </c>
       <c r="J24" s="0">
-        <v>1.1865425168447672</v>
+        <v>1.2392669097171591</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>577.55370000000005</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034699356249135</v>
       </c>
       <c r="F25" s="0">
-        <v>2.5370717517776349</v>
+        <v>2.5346993562491349</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5370717517776349</v>
+        <v>2.5346993562491349</v>
       </c>
       <c r="H25" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534699356249135</v>
       </c>
       <c r="I25" s="0">
-        <v>2.0370717517776349</v>
+        <v>2.0346993562491349</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0370717517776349</v>
+        <v>2.0346993562491349</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>688.17229999999995</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.94760996847609</v>
+        <v>20.850937274941149</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.30239003152390964</v>
+        <v>-0.39906272505885099</v>
       </c>
       <c r="G26" s="0">
-        <v>0.30239003152390964</v>
+        <v>0.39906272505885099</v>
       </c>
       <c r="H26" s="0">
-        <v>20.44760996847609</v>
+        <v>20.350937274941149</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.80239003152390964</v>
+        <v>-0.89906272505885099</v>
       </c>
       <c r="J26" s="0">
-        <v>0.80239003152390964</v>
+        <v>0.89906272505885099</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>638.71429999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079490635595949</v>
       </c>
       <c r="F27" s="0">
-        <v>1.8371086038769349</v>
+        <v>1.8294906355959491</v>
       </c>
       <c r="G27" s="0">
-        <v>1.8371086038769349</v>
+        <v>1.8294906355959491</v>
       </c>
       <c r="H27" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579490635595949</v>
       </c>
       <c r="I27" s="0">
-        <v>1.3371086038769349</v>
+        <v>1.3294906355959491</v>
       </c>
       <c r="J27" s="0">
-        <v>1.3371086038769349</v>
+        <v>1.3294906355959491</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>676.74940000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.998923987792811</v>
+        <v>20.989479636660242</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.75107601220718934</v>
+        <v>-0.76052036333975792</v>
       </c>
       <c r="G28" s="0">
-        <v>0.75107601220718934</v>
+        <v>0.76052036333975792</v>
       </c>
       <c r="H28" s="0">
-        <v>20.498923987792811</v>
+        <v>20.489479636660242</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2510760122071893</v>
+        <v>-1.2605203633397579</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2510760122071893</v>
+        <v>1.2605203633397579</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>353.73129999999998</v>
+        <v>354.31049999999999</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079496680892909</v>
       </c>
       <c r="F29" s="0">
-        <v>0.33710860387693486</v>
+        <v>0.32949668089290896</v>
       </c>
       <c r="G29" s="0">
-        <v>0.33710860387693486</v>
+        <v>0.32949668089290896</v>
       </c>
       <c r="H29" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579496680892909</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.16289139612306514</v>
+        <v>-0.17050331910709104</v>
       </c>
       <c r="J29" s="0">
-        <v>0.16289139612306514</v>
+        <v>0.17050331910709104</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>683.81759999999997</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.37279306539817</v>
+        <v>21.241270210865771</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.12720693460182986</v>
+        <v>-0.25872978913422884</v>
       </c>
       <c r="G30" s="0">
-        <v>0.12720693460182986</v>
+        <v>0.25872978913422884</v>
       </c>
       <c r="H30" s="0">
-        <v>20.87279306539817</v>
+        <v>20.741270210865771</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.62720693460182986</v>
+        <v>-0.75872978913422884</v>
       </c>
       <c r="J30" s="0">
-        <v>0.62720693460182986</v>
+        <v>0.75872978913422884</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1356.9842000000001</v>
+        <v>1353.5838000000001</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.415408456872417</v>
+        <v>21.241701396818737</v>
       </c>
       <c r="F31" s="0">
-        <v>1.9154084568724166</v>
+        <v>1.7417013968187369</v>
       </c>
       <c r="G31" s="0">
-        <v>1.9154084568724166</v>
+        <v>1.7417013968187369</v>
       </c>
       <c r="H31" s="0">
-        <v>20.915408456872417</v>
+        <v>20.741701396818737</v>
       </c>
       <c r="I31" s="0">
-        <v>1.4154084568724166</v>
+        <v>1.2417013968187369</v>
       </c>
       <c r="J31" s="0">
-        <v>1.4154084568724166</v>
+        <v>1.2417013968187369</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1312.2254</v>
+        <v>1324.2094</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.412588967744377</v>
+        <v>21.241682465478281</v>
       </c>
       <c r="F32" s="0">
-        <v>1.9125889677443766</v>
+        <v>1.7416824654782808</v>
       </c>
       <c r="G32" s="0">
-        <v>1.9125889677443766</v>
+        <v>1.7416824654782808</v>
       </c>
       <c r="H32" s="0">
-        <v>20.912588967744377</v>
+        <v>20.741682465478281</v>
       </c>
       <c r="I32" s="0">
-        <v>1.4125889677443766</v>
+        <v>1.2416824654782808</v>
       </c>
       <c r="J32" s="0">
-        <v>1.4125889677443766</v>
+        <v>1.2416824654782808</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,28 +1854,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1359.0623000000001</v>
+        <v>1370.5188000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.037071751777635</v>
+        <v>21.035267427897239</v>
       </c>
       <c r="F33" s="0">
-        <v>0.037071751777634887</v>
+        <v>0.03526742789723869</v>
       </c>
       <c r="G33" s="0">
-        <v>0.037071751777634887</v>
+        <v>0.03526742789723869</v>
       </c>
       <c r="H33" s="0">
-        <v>20.537071751777635</v>
+        <v>20.535267427897239</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.46292824822236511</v>
+        <v>-0.46473257210276131</v>
       </c>
       <c r="J33" s="0">
-        <v>0.46292824822236511</v>
+        <v>0.46473257210276131</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>595.53899999999999</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>20.947064538233313</v>
+        <v>21.029440448820306</v>
       </c>
       <c r="F34" s="0">
-        <v>0.69706453823331316</v>
+        <v>0.77944044882030639</v>
       </c>
       <c r="G34" s="0">
-        <v>0.69706453823331316</v>
+        <v>0.77944044882030639</v>
       </c>
       <c r="H34" s="0">
-        <v>20.447064538233313</v>
+        <v>20.529440448820306</v>
       </c>
       <c r="I34" s="0">
-        <v>0.19706453823331316</v>
+        <v>0.27944044882030639</v>
       </c>
       <c r="J34" s="0">
-        <v>0.19706453823331316</v>
+        <v>0.27944044882030639</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>620.18640000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034729893081611</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.46292824822236511</v>
+        <v>-0.4652701069183891</v>
       </c>
       <c r="G35" s="0">
-        <v>0.46292824822236511</v>
+        <v>0.4652701069183891</v>
       </c>
       <c r="H35" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534729893081611</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.96292824822236511</v>
+        <v>-0.9652701069183891</v>
       </c>
       <c r="J35" s="0">
-        <v>0.96292824822236511</v>
+        <v>0.9652701069183891</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>589.86860000000001</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034708177070446</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5370717517776349</v>
+        <v>1.5347081770704456</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5370717517776349</v>
+        <v>1.5347081770704456</v>
       </c>
       <c r="H36" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534708177070446</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0370717517776349</v>
+        <v>1.0347081770704456</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0370717517776349</v>
+        <v>1.0347081770704456</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>724.63610000000006</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079500489758036</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.9128913961230651</v>
+        <v>-3.9204995102419637</v>
       </c>
       <c r="G37" s="0">
-        <v>3.9128913961230651</v>
+        <v>3.9204995102419637</v>
       </c>
       <c r="H37" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579500489758036</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.4128913961230651</v>
+        <v>-4.4204995102419637</v>
       </c>
       <c r="J37" s="0">
-        <v>4.4128913961230651</v>
+        <v>4.4204995102419637</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>598.2287</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.998870632899816</v>
+        <v>20.989298479721924</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9988706328998163</v>
+        <v>1.9892984797219242</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9988706328998163</v>
+        <v>1.9892984797219242</v>
       </c>
       <c r="H38" s="0">
-        <v>20.498870632899816</v>
+        <v>20.489298479721924</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4988706328998163</v>
+        <v>1.4892984797219242</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4988706328998163</v>
+        <v>1.4892984797219242</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>681.9153</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.947610042165913</v>
+        <v>20.851046904066745</v>
       </c>
       <c r="F39" s="0">
-        <v>1.9476100421659126</v>
+        <v>1.8510469040667452</v>
       </c>
       <c r="G39" s="0">
-        <v>1.9476100421659126</v>
+        <v>1.8510469040667452</v>
       </c>
       <c r="H39" s="0">
-        <v>20.447610042165913</v>
+        <v>20.351046904066745</v>
       </c>
       <c r="I39" s="0">
-        <v>1.4476100421659126</v>
+        <v>1.3510469040667452</v>
       </c>
       <c r="J39" s="0">
-        <v>1.4476100421659126</v>
+        <v>1.3510469040667452</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1193.8898999999999</v>
+        <v>1171.8478</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.2252693133875</v>
+        <v>21.239649784434693</v>
       </c>
       <c r="F40" s="0">
-        <v>0.22526931338749989</v>
+        <v>0.2396497844346932</v>
       </c>
       <c r="G40" s="0">
-        <v>0.22526931338749989</v>
+        <v>0.2396497844346932</v>
       </c>
       <c r="H40" s="0">
-        <v>20.7252693133875</v>
+        <v>20.739649784434693</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.27473068661250011</v>
+        <v>-0.2603502155653068</v>
       </c>
       <c r="J40" s="0">
-        <v>0.27473068661250011</v>
+        <v>0.2603502155653068</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>665.75360000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.19181181567577</v>
+        <v>21.239323723502011</v>
       </c>
       <c r="F41" s="0">
-        <v>0.69181181567576999</v>
+        <v>0.73932372350201092</v>
       </c>
       <c r="G41" s="0">
-        <v>0.69181181567576999</v>
+        <v>0.73932372350201092</v>
       </c>
       <c r="H41" s="0">
-        <v>20.69181181567577</v>
+        <v>20.739323723502011</v>
       </c>
       <c r="I41" s="0">
-        <v>0.19181181567576999</v>
+        <v>0.23932372350201092</v>
       </c>
       <c r="J41" s="0">
-        <v>0.19181181567576999</v>
+        <v>0.23932372350201092</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>340.92939999999999</v>
+        <v>343.99220000000003</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.087108603876935</v>
+        <v>21.07949657476739</v>
       </c>
       <c r="F42" s="0">
-        <v>1.8371086038769349</v>
+        <v>1.8294965747673899</v>
       </c>
       <c r="G42" s="0">
-        <v>1.8371086038769349</v>
+        <v>1.8294965747673899</v>
       </c>
       <c r="H42" s="0">
-        <v>20.587108603876935</v>
+        <v>20.57949657476739</v>
       </c>
       <c r="I42" s="0">
-        <v>1.3371086038769349</v>
+        <v>1.3294965747673899</v>
       </c>
       <c r="J42" s="0">
-        <v>1.3371086038769349</v>
+        <v>1.3294965747673899</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>584.32039999999995</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.998859574151755</v>
+        <v>20.989266397443217</v>
       </c>
       <c r="F43" s="0">
-        <v>0.99885957415175497</v>
+        <v>0.98926639744321676</v>
       </c>
       <c r="G43" s="0">
-        <v>0.99885957415175497</v>
+        <v>0.98926639744321676</v>
       </c>
       <c r="H43" s="0">
-        <v>20.498859574151755</v>
+        <v>20.489266397443217</v>
       </c>
       <c r="I43" s="0">
-        <v>0.49885957415175497</v>
+        <v>0.48926639744321676</v>
       </c>
       <c r="J43" s="0">
-        <v>0.49885957415175497</v>
+        <v>0.48926639744321676</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>660.15719999999999</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.947609311191975</v>
+        <v>20.851428155346923</v>
       </c>
       <c r="F44" s="0">
-        <v>0.94760931119197522</v>
+        <v>0.85142815534692318</v>
       </c>
       <c r="G44" s="0">
-        <v>0.94760931119197522</v>
+        <v>0.85142815534692318</v>
       </c>
       <c r="H44" s="0">
-        <v>20.447609311191975</v>
+        <v>20.351428155346923</v>
       </c>
       <c r="I44" s="0">
-        <v>0.44760931119197522</v>
+        <v>0.35142815534692318</v>
       </c>
       <c r="J44" s="0">
-        <v>0.44760931119197522</v>
+        <v>0.35142815534692318</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>581.95590000000004</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034702509417162</v>
       </c>
       <c r="F45" s="0">
-        <v>1.0370717517776349</v>
+        <v>1.034702509417162</v>
       </c>
       <c r="G45" s="0">
-        <v>1.0370717517776349</v>
+        <v>1.034702509417162</v>
       </c>
       <c r="H45" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534702509417162</v>
       </c>
       <c r="I45" s="0">
-        <v>0.53707175177763489</v>
+        <v>0.53470250941716202</v>
       </c>
       <c r="J45" s="0">
-        <v>0.53707175177763489</v>
+        <v>0.53470250941716202</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1457.3396</v>
+        <v>1432.1427000000001</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.947625671113904</v>
+        <v>20.837927822793482</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.0523743288860956</v>
+        <v>-1.1620721772065181</v>
       </c>
       <c r="G46" s="0">
-        <v>1.0523743288860956</v>
+        <v>1.1620721772065181</v>
       </c>
       <c r="H46" s="0">
-        <v>20.447625671113904</v>
+        <v>20.337927822793482</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.5523743288860956</v>
+        <v>-1.6620721772065181</v>
       </c>
       <c r="J46" s="0">
-        <v>1.5523743288860956</v>
+        <v>1.6620721772065181</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1394.6958999999999</v>
+        <v>1393.6792</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.947624390508061</v>
+        <v>20.838599116644893</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.0523756094919392</v>
+        <v>-1.1614008833551068</v>
       </c>
       <c r="G47" s="0">
-        <v>1.0523756094919392</v>
+        <v>1.1614008833551068</v>
       </c>
       <c r="H47" s="0">
-        <v>20.447624390508061</v>
+        <v>20.338599116644893</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.5523756094919392</v>
+        <v>-1.6614008833551068</v>
       </c>
       <c r="J47" s="0">
-        <v>1.5523756094919392</v>
+        <v>1.6614008833551068</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1393.5521000000001</v>
+        <v>1418.9514999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.037071751777635</v>
+        <v>21.035302130029937</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.9629282482223651</v>
+        <v>-1.9646978699700632</v>
       </c>
       <c r="G48" s="0">
-        <v>1.9629282482223651</v>
+        <v>1.9646978699700632</v>
       </c>
       <c r="H48" s="0">
-        <v>20.537071751777635</v>
+        <v>20.535302130029937</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.4629282482223651</v>
+        <v>-2.4646978699700632</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4629282482223651</v>
+        <v>2.4646978699700632</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1328.9452000000001</v>
+        <v>1319.8444999999999</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.037071751777635</v>
+        <v>21.035231120257059</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.71292824822236511</v>
+        <v>-0.71476887974294101</v>
       </c>
       <c r="G49" s="0">
-        <v>0.71292824822236511</v>
+        <v>0.71476887974294101</v>
       </c>
       <c r="H49" s="0">
-        <v>20.537071751777635</v>
+        <v>20.535231120257059</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.2129282482223651</v>
+        <v>-1.214768879742941</v>
       </c>
       <c r="J49" s="0">
-        <v>1.2129282482223651</v>
+        <v>1.214768879742941</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1373.3529000000001</v>
+        <v>1370.9471000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>20.999360031488319</v>
+        <v>20.99108297774454</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.50063996851168113</v>
+        <v>-0.50891702225545998</v>
       </c>
       <c r="G50" s="0">
-        <v>0.50063996851168113</v>
+        <v>0.50891702225545998</v>
       </c>
       <c r="H50" s="0">
-        <v>20.499360031488319</v>
+        <v>20.49108297774454</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.0006399685116811</v>
+        <v>-1.00891702225546</v>
       </c>
       <c r="J50" s="0">
-        <v>1.0006399685116811</v>
+        <v>1.00891702225546</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1232.3471999999999</v>
+        <v>1230.9086</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.227715868667119</v>
+        <v>21.239687798628136</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0277158686671193</v>
+        <v>2.0396877986281368</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0277158686671193</v>
+        <v>2.0396877986281368</v>
       </c>
       <c r="H51" s="0">
-        <v>20.727715868667119</v>
+        <v>20.739687798628136</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5277158686671193</v>
+        <v>1.5396877986281368</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5277158686671193</v>
+        <v>1.5396877986281368</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1151.9466</v>
+        <v>1142.3658</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.037071751777635</v>
+        <v>21.035103963583392</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5370717517776349</v>
+        <v>3.5351039635833921</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5370717517776349</v>
+        <v>3.5351039635833921</v>
       </c>
       <c r="H52" s="0">
-        <v>20.537071751777635</v>
+        <v>20.535103963583392</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0370717517776349</v>
+        <v>3.0351039635833921</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0370717517776349</v>
+        <v>3.0351039635833921</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1179.067</v>
+        <v>1183.6578999999999</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079496240431325</v>
       </c>
       <c r="F53" s="0">
-        <v>2.6871086038769363</v>
+        <v>2.6794962404313267</v>
       </c>
       <c r="G53" s="0">
-        <v>2.6871086038769363</v>
+        <v>2.6794962404313267</v>
       </c>
       <c r="H53" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579496240431325</v>
       </c>
       <c r="I53" s="0">
-        <v>2.1871086038769363</v>
+        <v>2.1794962404313267</v>
       </c>
       <c r="J53" s="0">
-        <v>2.1871086038769363</v>
+        <v>2.1794962404313267</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.4477999999999</v>
+        <v>1127.7965999999999</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.999204320444882</v>
+        <v>20.990521132072416</v>
       </c>
       <c r="F54" s="0">
-        <v>1.9992043204448819</v>
+        <v>1.9905211320724163</v>
       </c>
       <c r="G54" s="0">
-        <v>1.9992043204448819</v>
+        <v>1.9905211320724163</v>
       </c>
       <c r="H54" s="0">
-        <v>20.499204320444882</v>
+        <v>20.490521132072416</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4992043204448819</v>
+        <v>1.4905211320724163</v>
       </c>
       <c r="J54" s="0">
-        <v>1.4992043204448819</v>
+        <v>1.4905211320724163</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>600.21460000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.99887087779241</v>
+        <v>20.989303060746458</v>
       </c>
       <c r="F55" s="0">
-        <v>1.4988708777924096</v>
+        <v>1.4893030607464581</v>
       </c>
       <c r="G55" s="0">
-        <v>1.4988708777924096</v>
+        <v>1.4893030607464581</v>
       </c>
       <c r="H55" s="0">
-        <v>20.49887087779241</v>
+        <v>20.489303060746458</v>
       </c>
       <c r="I55" s="0">
-        <v>0.99887087779240957</v>
+        <v>0.98930306074645813</v>
       </c>
       <c r="J55" s="0">
-        <v>0.99887087779240957</v>
+        <v>0.98930306074645813</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>684.51480000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.947610759557691</v>
+        <v>20.851001357713411</v>
       </c>
       <c r="F56" s="0">
-        <v>0.44761075955769059</v>
+        <v>0.35100135771341101</v>
       </c>
       <c r="G56" s="0">
-        <v>0.44761075955769059</v>
+        <v>0.35100135771341101</v>
       </c>
       <c r="H56" s="0">
-        <v>20.447610759557691</v>
+        <v>20.351001357713411</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.052389240442309415</v>
+        <v>-0.14899864228658899</v>
       </c>
       <c r="J56" s="0">
-        <v>0.052389240442309415</v>
+        <v>0.14899864228658899</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>632.78740000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.037071751777635</v>
+        <v>21.03745914756411</v>
       </c>
       <c r="F57" s="0">
-        <v>0.037071751777634887</v>
+        <v>0.037459147564110395</v>
       </c>
       <c r="G57" s="0">
-        <v>0.037071751777634887</v>
+        <v>0.037459147564110395</v>
       </c>
       <c r="H57" s="0">
-        <v>20.537071751777635</v>
+        <v>20.53745914756411</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.46292824822236511</v>
+        <v>-0.4625408524358896</v>
       </c>
       <c r="J57" s="0">
-        <v>0.46292824822236511</v>
+        <v>0.4625408524358896</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1120.8548000000001</v>
+        <v>1105.7334000000001</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079504409413847</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.4128913961230651</v>
+        <v>-2.4204955905861532</v>
       </c>
       <c r="G58" s="0">
-        <v>2.4128913961230651</v>
+        <v>2.4204955905861532</v>
       </c>
       <c r="H58" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579504409413847</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.9128913961230651</v>
+        <v>-2.9204955905861532</v>
       </c>
       <c r="J58" s="0">
-        <v>2.9128913961230651</v>
+        <v>2.9204955905861532</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>665.27829999999995</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.371669026113278</v>
+        <v>21.241258287479297</v>
       </c>
       <c r="F59" s="0">
-        <v>0.87166902611327757</v>
+        <v>0.74125828747929745</v>
       </c>
       <c r="G59" s="0">
-        <v>0.87166902611327757</v>
+        <v>0.74125828747929745</v>
       </c>
       <c r="H59" s="0">
-        <v>20.871669026113278</v>
+        <v>20.741258287479297</v>
       </c>
       <c r="I59" s="0">
-        <v>0.37166902611327757</v>
+        <v>0.24125828747929745</v>
       </c>
       <c r="J59" s="0">
-        <v>0.37166902611327757</v>
+        <v>0.24125828747929745</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>655.14710000000002</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.99909115038988</v>
+        <v>20.991905897319786</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.50090884961011994</v>
+        <v>-0.50809410268021438</v>
       </c>
       <c r="G60" s="0">
-        <v>0.50090884961011994</v>
+        <v>0.50809410268021438</v>
       </c>
       <c r="H60" s="0">
-        <v>20.49909115038988</v>
+        <v>20.491905897319786</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.00090884961012</v>
+        <v>-1.0080941026802144</v>
       </c>
       <c r="J60" s="0">
-        <v>1.00090884961012</v>
+        <v>1.0080941026802144</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>642.19590000000005</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079499641845601</v>
       </c>
       <c r="F61" s="0">
-        <v>1.0871086038769349</v>
+        <v>1.0794996418456009</v>
       </c>
       <c r="G61" s="0">
-        <v>1.0871086038769349</v>
+        <v>1.0794996418456009</v>
       </c>
       <c r="H61" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579499641845601</v>
       </c>
       <c r="I61" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949964184560088</v>
       </c>
       <c r="J61" s="0">
-        <v>0.58710860387693487</v>
+        <v>0.57949964184560088</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>671.02829999999995</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.087108603876935</v>
+        <v>21.079499938392061</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.9128913961230651</v>
+        <v>-1.9205000616079389</v>
       </c>
       <c r="G62" s="0">
-        <v>1.9128913961230651</v>
+        <v>1.9205000616079389</v>
       </c>
       <c r="H62" s="0">
-        <v>20.587108603876935</v>
+        <v>20.579499938392061</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.4128913961230651</v>
+        <v>-2.4205000616079389</v>
       </c>
       <c r="J62" s="0">
-        <v>2.4128913961230651</v>
+        <v>2.4205000616079389</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>658.74609999999996</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>20.94706601717094</v>
+        <v>21.028329228159898</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.55293398282906026</v>
+        <v>-0.47167077184010253</v>
       </c>
       <c r="G63" s="0">
-        <v>0.55293398282906026</v>
+        <v>0.47167077184010253</v>
       </c>
       <c r="H63" s="0">
-        <v>20.44706601717094</v>
+        <v>20.528329228159898</v>
       </c>
       <c r="I63" s="0">
-        <v>-1.0529339828290603</v>
+        <v>-0.97167077184010253</v>
       </c>
       <c r="J63" s="0">
-        <v>1.0529339828290603</v>
+        <v>0.97167077184010253</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>421.81869999999998</v>
+        <v>418.81540000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.998757547038693</v>
+        <v>20.988884775856075</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.5012424529613071</v>
+        <v>-1.511115224143925</v>
       </c>
       <c r="G64" s="0">
-        <v>1.5012424529613071</v>
+        <v>1.511115224143925</v>
       </c>
       <c r="H64" s="0">
-        <v>20.498757547038693</v>
+        <v>20.488884775856075</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.0012424529613071</v>
+        <v>-2.011115224143925</v>
       </c>
       <c r="J64" s="0">
-        <v>2.0012424529613071</v>
+        <v>2.011115224143925</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>593.42259999999999</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.367165534869336</v>
+        <v>21.241212079047436</v>
       </c>
       <c r="F65" s="0">
-        <v>2.1171655348693363</v>
+        <v>1.9912120790474361</v>
       </c>
       <c r="G65" s="0">
-        <v>2.1171655348693363</v>
+        <v>1.9912120790474361</v>
       </c>
       <c r="H65" s="0">
-        <v>20.867165534869336</v>
+        <v>20.741212079047436</v>
       </c>
       <c r="I65" s="0">
-        <v>1.6171655348693363</v>
+        <v>1.4912120790474361</v>
       </c>
       <c r="J65" s="0">
-        <v>1.6171655348693363</v>
+        <v>1.4912120790474361</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>709.44029999999998</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034793825521714</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4629282482223651</v>
+        <v>-2.4652061744782863</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4629282482223651</v>
+        <v>2.4652061744782863</v>
       </c>
       <c r="H66" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534793825521714</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9629282482223651</v>
+        <v>-2.9652061744782863</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9629282482223651</v>
+        <v>2.9652061744782863</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>625.83199999999999</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.037071751777635</v>
+        <v>21.034733936940871</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.46292824822236511</v>
+        <v>-0.46526606305912921</v>
       </c>
       <c r="G67" s="0">
-        <v>0.46292824822236511</v>
+        <v>0.46526606305912921</v>
       </c>
       <c r="H67" s="0">
-        <v>20.537071751777635</v>
+        <v>20.534733936940871</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.96292824822236511</v>
+        <v>-0.96526606305912921</v>
       </c>
       <c r="J67" s="0">
-        <v>0.96292824822236511</v>
+        <v>0.96526606305912921</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>879.03800000000001</v>
+        <v>889.9828</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.037071751777635</v>
+        <v>21.03764347620605</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0370717517776349</v>
+        <v>2.0376434762060498</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0370717517776349</v>
+        <v>2.0376434762060498</v>
       </c>
       <c r="H68" s="0">
-        <v>20.537071751777635</v>
+        <v>20.53764347620605</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5370717517776349</v>
+        <v>1.5376434762060498</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5370717517776349</v>
+        <v>1.5376434762060498</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3479,13 +3479,13 @@
         <v>1.476</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8200000000000001</v>
+        <v>1.821</v>
       </c>
       <c r="D2" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.049000000000000002</v>
       </c>
       <c r="E2" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.058999999999999997</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3495,19 +3495,19 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="C3" s="0">
-        <v>0.019</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="D3" s="0">
         <v>0.016</v>
       </c>
       <c r="E3" s="0">
-        <v>0.027</v>
+        <v>0.025999999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>0.80000000000000004</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G3" s="0">
         <v>0.69999999999999996</v>
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.484</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.431</v>
+        <v>-0.441</v>
       </c>
       <c r="F5" s="0">
-        <v>39</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="G5" s="0">
-        <v>44.799999999999997</v>
+        <v>44.299999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.556</v>
+        <v>1.5569999999999999</v>
       </c>
       <c r="C6" s="0">
         <v>1.907</v>
       </c>
       <c r="D6" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.041000000000000002</v>
       </c>
       <c r="E6" s="0">
-        <v>0.002</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3567,12 +3567,12 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.5800000000000001</v>
+        <v>1.5820000000000001</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.498</v>
+        <v>-0.497</v>
       </c>
       <c r="F7" s="0">
         <v>37.299999999999997</v>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>20.5014</v>
+        <v>20.521599999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>0.65169999999999995</v>
+        <v>0.64939999999999998</v>
       </c>
       <c r="D2" s="0">
-        <v>31.457999999999999</v>
+        <v>31.603000000000002</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3711,10 +3711,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.55700000000000005</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E3" s="0">
-        <v>0.5796</v>
+        <v>0.60160000000000002</v>
       </c>
     </row>
     <row r="4">
@@ -3722,16 +3722,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>0.42659999999999998</v>
+        <v>0.42609999999999998</v>
       </c>
       <c r="C4" s="0">
-        <v>0.45379999999999998</v>
+        <v>0.45429999999999998</v>
       </c>
       <c r="D4" s="0">
-        <v>0.93999999999999995</v>
+        <v>0.93799999999999995</v>
       </c>
       <c r="E4" s="0">
-        <v>0.3508</v>
+        <v>0.3518</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_性別.xlsx
@@ -490,28 +490,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>405.481</v>
+        <v>408.47719999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>20.991328932879696</v>
+        <v>20.989982808619139</v>
       </c>
       <c r="F2" s="0">
-        <v>-2.0086710671203036</v>
+        <v>-2.0100171913808609</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0086710671203036</v>
+        <v>2.0100171913808609</v>
       </c>
       <c r="H2" s="0">
-        <v>20.491328932879696</v>
+        <v>20.489982808619139</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.5086710671203036</v>
+        <v>-2.5100171913808609</v>
       </c>
       <c r="J2" s="0">
-        <v>2.5086710671203036</v>
+        <v>2.5100171913808609</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -534,28 +534,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.36530000000005</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.239284774403441</v>
+        <v>21.238605582850987</v>
       </c>
       <c r="F3" s="0">
-        <v>0.23928477440344054</v>
+        <v>0.23860558285098676</v>
       </c>
       <c r="G3" s="0">
-        <v>0.23928477440344054</v>
+        <v>0.23860558285098676</v>
       </c>
       <c r="H3" s="0">
-        <v>20.739284774403441</v>
+        <v>20.738605582850987</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.26071522559655946</v>
+        <v>-0.26139441714901324</v>
       </c>
       <c r="J3" s="0">
-        <v>0.26071522559655946</v>
+        <v>0.26139441714901324</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -578,28 +578,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>740.86210000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.079500656645408</v>
+        <v>21.078743951925258</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4204993433545923</v>
+        <v>-2.421256048074742</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4204993433545923</v>
+        <v>2.421256048074742</v>
       </c>
       <c r="H4" s="0">
-        <v>20.579500656645408</v>
+        <v>20.578743951925258</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9204993433545923</v>
+        <v>-2.921256048074742</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9204993433545923</v>
+        <v>2.921256048074742</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -622,28 +622,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>580.86249999999996</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.989258421389117</v>
+        <v>20.986431694894083</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.010741578610883096</v>
+        <v>-0.013568305105916778</v>
       </c>
       <c r="G5" s="0">
-        <v>0.010741578610883096</v>
+        <v>0.013568305105916778</v>
       </c>
       <c r="H5" s="0">
-        <v>20.489258421389117</v>
+        <v>20.486431694894083</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.5107415786108831</v>
+        <v>-0.51356830510591678</v>
       </c>
       <c r="J5" s="0">
-        <v>0.5107415786108831</v>
+        <v>0.51356830510591678</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -666,28 +666,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>620.73389999999995</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.239294687759465</v>
+        <v>21.2386149982398</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.26070531224053539</v>
+        <v>-0.26138500176019974</v>
       </c>
       <c r="G6" s="0">
-        <v>0.26070531224053539</v>
+        <v>0.26138500176019974</v>
       </c>
       <c r="H6" s="0">
-        <v>20.739294687759465</v>
+        <v>20.7386149982398</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.76070531224053539</v>
+        <v>-0.76138500176019974</v>
       </c>
       <c r="J6" s="0">
-        <v>0.76070531224053539</v>
+        <v>0.76138500176019974</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>711.67399999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>20.989560229304299</v>
+        <v>20.986960927522361</v>
       </c>
       <c r="F7" s="0">
-        <v>-1.0104397706957009</v>
+        <v>-1.013039072477639</v>
       </c>
       <c r="G7" s="0">
-        <v>1.0104397706957009</v>
+        <v>1.013039072477639</v>
       </c>
       <c r="H7" s="0">
-        <v>20.489560229304299</v>
+        <v>20.486960927522361</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.5104397706957009</v>
+        <v>-1.513039072477639</v>
       </c>
       <c r="J7" s="0">
-        <v>1.5104397706957009</v>
+        <v>1.513039072477639</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -754,28 +754,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>757.66719999999998</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.037548648307567</v>
+        <v>21.038051191638356</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9624513516924331</v>
+        <v>-3.9619488083616439</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9624513516924331</v>
+        <v>3.9619488083616439</v>
       </c>
       <c r="H8" s="0">
-        <v>20.537548648307567</v>
+        <v>20.538051191638356</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.4624513516924331</v>
+        <v>-4.4619488083616439</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4624513516924331</v>
+        <v>4.4619488083616439</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -798,28 +798,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>390.43310000000002</v>
+        <v>384.85610000000003</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.241081580510237</v>
+        <v>21.240457369214958</v>
       </c>
       <c r="F9" s="0">
-        <v>0.74108158051023665</v>
+        <v>0.74045736921495831</v>
       </c>
       <c r="G9" s="0">
-        <v>0.74108158051023665</v>
+        <v>0.74045736921495831</v>
       </c>
       <c r="H9" s="0">
-        <v>20.741081580510237</v>
+        <v>20.740457369214958</v>
       </c>
       <c r="I9" s="0">
-        <v>0.24108158051023665</v>
+        <v>0.24045736921495831</v>
       </c>
       <c r="J9" s="0">
-        <v>0.24108158051023665</v>
+        <v>0.24045736921495831</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -842,28 +842,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1263.4103</v>
+        <v>1296.7855999999999</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.241643288133851</v>
+        <v>21.241054020262144</v>
       </c>
       <c r="F10" s="0">
-        <v>0.24164328813385083</v>
+        <v>0.24105402026214406</v>
       </c>
       <c r="G10" s="0">
-        <v>0.24164328813385083</v>
+        <v>0.24105402026214406</v>
       </c>
       <c r="H10" s="0">
-        <v>20.741643288133851</v>
+        <v>20.741054020262144</v>
       </c>
       <c r="I10" s="0">
-        <v>-0.25835671186614917</v>
+        <v>-0.25894597973785594</v>
       </c>
       <c r="J10" s="0">
-        <v>0.25835671186614917</v>
+        <v>0.25894597973785594</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>0</v>
@@ -886,28 +886,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>319.74869999999999</v>
+        <v>320.06220000000002</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.988656491413686</v>
+        <v>20.985354529021382</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9886564914136855</v>
+        <v>2.9853545290213823</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9886564914136855</v>
+        <v>2.9853545290213823</v>
       </c>
       <c r="H11" s="0">
-        <v>20.488656491413686</v>
+        <v>20.485354529021382</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4886564914136855</v>
+        <v>2.4853545290213823</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4886564914136855</v>
+        <v>2.4853545290213823</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -930,28 +930,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>718.36379999999997</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.850408337144373</v>
+        <v>20.846150947162055</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.1495916628556273</v>
+        <v>-4.1538490528379448</v>
       </c>
       <c r="G12" s="0">
-        <v>4.1495916628556273</v>
+        <v>4.1538490528379448</v>
       </c>
       <c r="H12" s="0">
-        <v>20.350408337144373</v>
+        <v>20.346150947162055</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.6495916628556273</v>
+        <v>-4.6538490528379448</v>
       </c>
       <c r="J12" s="0">
-        <v>4.6495916628556273</v>
+        <v>4.6538490528379448</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -974,28 +974,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>669.91160000000002</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.851257230981329</v>
+        <v>20.837492595728481</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.6487427690186713</v>
+        <v>-1.6625074042715191</v>
       </c>
       <c r="G13" s="0">
-        <v>1.6487427690186713</v>
+        <v>1.6625074042715191</v>
       </c>
       <c r="H13" s="0">
-        <v>20.351257230981329</v>
+        <v>20.337492595728481</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.1487427690186713</v>
+        <v>-2.1625074042715191</v>
       </c>
       <c r="J13" s="0">
-        <v>2.1487427690186713</v>
+        <v>2.1625074042715191</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1018,28 +1018,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>672.01459999999997</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.079499948536338</v>
+        <v>21.078743082748858</v>
       </c>
       <c r="F14" s="0">
-        <v>0.57949994853633768</v>
+        <v>0.57874308274885777</v>
       </c>
       <c r="G14" s="0">
-        <v>0.57949994853633768</v>
+        <v>0.57874308274885777</v>
       </c>
       <c r="H14" s="0">
-        <v>20.579499948536338</v>
+        <v>20.578743082748858</v>
       </c>
       <c r="I14" s="0">
-        <v>0.079499948536337684</v>
+        <v>0.078743082748857773</v>
       </c>
       <c r="J14" s="0">
-        <v>0.079499948536337684</v>
+        <v>0.078743082748857773</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1062,28 +1062,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>585.0598</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>21.02962465008904</v>
+        <v>21.165636727763488</v>
       </c>
       <c r="F15" s="0">
-        <v>1.5296246500890405</v>
+        <v>1.6656367277634878</v>
       </c>
       <c r="G15" s="0">
-        <v>1.5296246500890405</v>
+        <v>1.6656367277634878</v>
       </c>
       <c r="H15" s="0">
-        <v>20.52962465008904</v>
+        <v>20.665636727763488</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0296246500890405</v>
+        <v>1.1656367277634878</v>
       </c>
       <c r="J15" s="0">
-        <v>1.0296246500890405</v>
+        <v>1.1656367277634878</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1106,28 +1106,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.17600000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.241227996414743</v>
+        <v>21.240614195001982</v>
       </c>
       <c r="F16" s="0">
-        <v>1.741227996414743</v>
+        <v>1.7406141950019816</v>
       </c>
       <c r="G16" s="0">
-        <v>1.741227996414743</v>
+        <v>1.7406141950019816</v>
       </c>
       <c r="H16" s="0">
-        <v>20.741227996414743</v>
+        <v>20.740614195001982</v>
       </c>
       <c r="I16" s="0">
-        <v>1.241227996414743</v>
+        <v>1.2406141950019816</v>
       </c>
       <c r="J16" s="0">
-        <v>1.241227996414743</v>
+        <v>1.2406141950019816</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1150,28 +1150,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1122.4987000000001</v>
+        <v>1128.8182999999999</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>21.079504581848052</v>
+        <v>21.078748296465193</v>
       </c>
       <c r="F17" s="0">
-        <v>2.5795045818480524</v>
+        <v>2.5787482964651929</v>
       </c>
       <c r="G17" s="0">
-        <v>2.5795045818480524</v>
+        <v>2.5787482964651929</v>
       </c>
       <c r="H17" s="0">
-        <v>20.579504581848052</v>
+        <v>20.578748296465193</v>
       </c>
       <c r="I17" s="0">
-        <v>2.0795045818480524</v>
+        <v>2.0787482964651929</v>
       </c>
       <c r="J17" s="0">
-        <v>2.0795045818480524</v>
+        <v>2.0787482964651929</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1194,28 +1194,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1459.4197999999999</v>
+        <v>1473.3333</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.837451851802516</v>
+        <v>20.920161970589611</v>
       </c>
       <c r="F18" s="0">
-        <v>-2.9125481481974838</v>
+        <v>-2.8298380294103893</v>
       </c>
       <c r="G18" s="0">
-        <v>2.9125481481974838</v>
+        <v>2.8298380294103893</v>
       </c>
       <c r="H18" s="0">
-        <v>20.337451851802516</v>
+        <v>20.420161970589611</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.4125481481974838</v>
+        <v>-3.3298380294103893</v>
       </c>
       <c r="J18" s="0">
-        <v>3.4125481481974838</v>
+        <v>3.3298380294103893</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1238,28 +1238,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>667.94280000000003</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.03476410060512</v>
+        <v>21.036175471516586</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2152358993948802</v>
+        <v>-1.2138245284834142</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2152358993948802</v>
+        <v>1.2138245284834142</v>
       </c>
       <c r="H19" s="0">
-        <v>20.53476410060512</v>
+        <v>20.536175471516586</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7152358993948802</v>
+        <v>-1.7138245284834142</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7152358993948802</v>
+        <v>1.7138245284834142</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1282,28 +1282,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>755.404</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>20.992137599187867</v>
+        <v>20.991399837986009</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.5078624008121331</v>
+        <v>-4.5086001620139911</v>
       </c>
       <c r="G20" s="0">
-        <v>4.5078624008121331</v>
+        <v>4.5086001620139911</v>
       </c>
       <c r="H20" s="0">
-        <v>20.492137599187867</v>
+        <v>20.491399837986009</v>
       </c>
       <c r="I20" s="0">
-        <v>-5.0078624008121331</v>
+        <v>-5.0086001620139911</v>
       </c>
       <c r="J20" s="0">
-        <v>5.0078624008121331</v>
+        <v>5.0086001620139911</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1326,28 +1326,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>344.29160000000002</v>
+        <v>349.81529999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.85696743230228</v>
+        <v>20.807647565761151</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.6430325676977198</v>
+        <v>-1.692352434238849</v>
       </c>
       <c r="G21" s="0">
-        <v>1.6430325676977198</v>
+        <v>1.692352434238849</v>
       </c>
       <c r="H21" s="0">
-        <v>20.35696743230228</v>
+        <v>20.307647565761151</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.1430325676977198</v>
+        <v>-2.192352434238849</v>
       </c>
       <c r="J21" s="0">
-        <v>2.1430325676977198</v>
+        <v>2.192352434238849</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1370,28 +1370,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>613.17560000000003</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>21.079499343366564</v>
+        <v>21.078742312876479</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.42050065663343617</v>
+        <v>-0.42125768712352141</v>
       </c>
       <c r="G22" s="0">
-        <v>0.42050065663343617</v>
+        <v>0.42125768712352141</v>
       </c>
       <c r="H22" s="0">
-        <v>20.579499343366564</v>
+        <v>20.578742312876479</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.92050065663343617</v>
+        <v>-0.92125768712352141</v>
       </c>
       <c r="J22" s="0">
-        <v>0.92050065663343617</v>
+        <v>0.92125768712352141</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1414,28 +1414,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>674.47910000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.079491003442506</v>
+        <v>21.078732639151191</v>
       </c>
       <c r="F23" s="0">
-        <v>1.0794910034425058</v>
+        <v>1.0787326391511911</v>
       </c>
       <c r="G23" s="0">
-        <v>1.0794910034425058</v>
+        <v>1.0787326391511911</v>
       </c>
       <c r="H23" s="0">
-        <v>20.579491003442506</v>
+        <v>20.578732639151191</v>
       </c>
       <c r="I23" s="0">
-        <v>0.57949100344250582</v>
+        <v>0.57873263915119111</v>
       </c>
       <c r="J23" s="0">
-        <v>0.57949100344250582</v>
+        <v>0.57873263915119111</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1458,28 +1458,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>577.67240000000004</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.239266909717159</v>
+        <v>21.238582824738131</v>
       </c>
       <c r="F24" s="0">
-        <v>1.7392669097171591</v>
+        <v>1.7385828247381312</v>
       </c>
       <c r="G24" s="0">
-        <v>1.7392669097171591</v>
+        <v>1.7385828247381312</v>
       </c>
       <c r="H24" s="0">
-        <v>20.739266909717159</v>
+        <v>20.738582824738131</v>
       </c>
       <c r="I24" s="0">
-        <v>1.2392669097171591</v>
+        <v>1.2385828247381312</v>
       </c>
       <c r="J24" s="0">
-        <v>1.2392669097171591</v>
+        <v>1.2385828247381312</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1502,28 +1502,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.55370000000005</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.034699356249135</v>
+        <v>21.036127618232566</v>
       </c>
       <c r="F25" s="0">
-        <v>2.5346993562491349</v>
+        <v>2.5361276182325661</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5346993562491349</v>
+        <v>2.5361276182325661</v>
       </c>
       <c r="H25" s="0">
-        <v>20.534699356249135</v>
+        <v>20.536127618232566</v>
       </c>
       <c r="I25" s="0">
-        <v>2.0346993562491349</v>
+        <v>2.0361276182325661</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0346993562491349</v>
+        <v>2.0361276182325661</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1546,28 +1546,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>688.17229999999995</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.850937274941149</v>
+        <v>20.840891260518575</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.39906272505885099</v>
+        <v>-0.40910873948142523</v>
       </c>
       <c r="G26" s="0">
-        <v>0.39906272505885099</v>
+        <v>0.40910873948142523</v>
       </c>
       <c r="H26" s="0">
-        <v>20.350937274941149</v>
+        <v>20.340891260518575</v>
       </c>
       <c r="I26" s="0">
-        <v>-0.89906272505885099</v>
+        <v>-0.90910873948142523</v>
       </c>
       <c r="J26" s="0">
-        <v>0.89906272505885099</v>
+        <v>0.90910873948142523</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1590,28 +1590,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>638.71429999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.079490635595949</v>
+        <v>21.078732361474121</v>
       </c>
       <c r="F27" s="0">
-        <v>1.8294906355959491</v>
+        <v>1.8287323614741204</v>
       </c>
       <c r="G27" s="0">
-        <v>1.8294906355959491</v>
+        <v>1.8287323614741204</v>
       </c>
       <c r="H27" s="0">
-        <v>20.579490635595949</v>
+        <v>20.578732361474121</v>
       </c>
       <c r="I27" s="0">
-        <v>1.3294906355959491</v>
+        <v>1.3287323614741204</v>
       </c>
       <c r="J27" s="0">
-        <v>1.3294906355959491</v>
+        <v>1.3287323614741204</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1634,28 +1634,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>676.74940000000004</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.989479636660242</v>
+        <v>20.986930838185131</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.76052036333975792</v>
+        <v>-0.76306916181486884</v>
       </c>
       <c r="G28" s="0">
-        <v>0.76052036333975792</v>
+        <v>0.76306916181486884</v>
       </c>
       <c r="H28" s="0">
-        <v>20.489479636660242</v>
+        <v>20.486930838185131</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2605203633397579</v>
+        <v>-1.2630691618148688</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2605203633397579</v>
+        <v>1.2630691618148688</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1678,28 +1678,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>354.31049999999999</v>
+        <v>353.71350000000001</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.079496680892909</v>
+        <v>21.07873923267374</v>
       </c>
       <c r="F29" s="0">
-        <v>0.32949668089290896</v>
+        <v>0.32873923267374039</v>
       </c>
       <c r="G29" s="0">
-        <v>0.32949668089290896</v>
+        <v>0.32873923267374039</v>
       </c>
       <c r="H29" s="0">
-        <v>20.579496680892909</v>
+        <v>20.57873923267374</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.17050331910709104</v>
+        <v>-0.17126076732625961</v>
       </c>
       <c r="J29" s="0">
-        <v>0.17050331910709104</v>
+        <v>0.17126076732625961</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1722,28 +1722,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.81759999999997</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.241270210865771</v>
+        <v>21.240656202353861</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.25872978913422884</v>
+        <v>-0.2593437976461388</v>
       </c>
       <c r="G30" s="0">
-        <v>0.25872978913422884</v>
+        <v>0.2593437976461388</v>
       </c>
       <c r="H30" s="0">
-        <v>20.741270210865771</v>
+        <v>20.740656202353861</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.75872978913422884</v>
+        <v>-0.7593437976461388</v>
       </c>
       <c r="J30" s="0">
-        <v>0.75872978913422884</v>
+        <v>0.7593437976461388</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1766,28 +1766,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1353.5838000000001</v>
+        <v>1374.7736</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.241701396818737</v>
+        <v>21.241105115005858</v>
       </c>
       <c r="F31" s="0">
-        <v>1.7417013968187369</v>
+        <v>1.7411051150058583</v>
       </c>
       <c r="G31" s="0">
-        <v>1.7417013968187369</v>
+        <v>1.7411051150058583</v>
       </c>
       <c r="H31" s="0">
-        <v>20.741701396818737</v>
+        <v>20.741105115005858</v>
       </c>
       <c r="I31" s="0">
-        <v>1.2417013968187369</v>
+        <v>1.2411051150058583</v>
       </c>
       <c r="J31" s="0">
-        <v>1.2417013968187369</v>
+        <v>1.2411051150058583</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1810,28 +1810,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1324.2094</v>
+        <v>1328.4146000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.241682465478281</v>
+        <v>21.241074740770664</v>
       </c>
       <c r="F32" s="0">
-        <v>1.7416824654782808</v>
+        <v>1.7410747407706637</v>
       </c>
       <c r="G32" s="0">
-        <v>1.7416824654782808</v>
+        <v>1.7410747407706637</v>
       </c>
       <c r="H32" s="0">
-        <v>20.741682465478281</v>
+        <v>20.741074740770664</v>
       </c>
       <c r="I32" s="0">
-        <v>1.2416824654782808</v>
+        <v>1.2410747407706637</v>
       </c>
       <c r="J32" s="0">
-        <v>1.2416824654782808</v>
+        <v>1.2410747407706637</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1854,28 +1854,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1370.5188000000001</v>
+        <v>1401.6427000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.035267427897239</v>
+        <v>21.036546694612966</v>
       </c>
       <c r="F33" s="0">
-        <v>0.03526742789723869</v>
+        <v>0.03654669461296578</v>
       </c>
       <c r="G33" s="0">
-        <v>0.03526742789723869</v>
+        <v>0.03654669461296578</v>
       </c>
       <c r="H33" s="0">
-        <v>20.535267427897239</v>
+        <v>20.536546694612966</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.46473257210276131</v>
+        <v>-0.46345330538703422</v>
       </c>
       <c r="J33" s="0">
-        <v>0.46473257210276131</v>
+        <v>0.46345330538703422</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1898,28 +1898,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>595.53899999999999</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>21.029440448820306</v>
+        <v>21.167384574549104</v>
       </c>
       <c r="F34" s="0">
-        <v>0.77944044882030639</v>
+        <v>0.91738457454910361</v>
       </c>
       <c r="G34" s="0">
-        <v>0.77944044882030639</v>
+        <v>0.91738457454910361</v>
       </c>
       <c r="H34" s="0">
-        <v>20.529440448820306</v>
+        <v>20.667384574549104</v>
       </c>
       <c r="I34" s="0">
-        <v>0.27944044882030639</v>
+        <v>0.41738457454910361</v>
       </c>
       <c r="J34" s="0">
-        <v>0.27944044882030639</v>
+        <v>0.41738457454910361</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1942,28 +1942,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>620.18640000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.034729893081611</v>
+        <v>21.036147333290081</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.4652701069183891</v>
+        <v>-0.46385266670991854</v>
       </c>
       <c r="G35" s="0">
-        <v>0.4652701069183891</v>
+        <v>0.46385266670991854</v>
       </c>
       <c r="H35" s="0">
-        <v>20.534729893081611</v>
+        <v>20.536147333290081</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.9652701069183891</v>
+        <v>-0.96385266670991854</v>
       </c>
       <c r="J35" s="0">
-        <v>0.9652701069183891</v>
+        <v>0.96385266670991854</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1986,28 +1986,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>589.86860000000001</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.034708177070446</v>
+        <v>21.036134830911248</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5347081770704456</v>
+        <v>1.5361348309112479</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5347081770704456</v>
+        <v>1.5361348309112479</v>
       </c>
       <c r="H36" s="0">
-        <v>20.534708177070446</v>
+        <v>20.536134830911248</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0347081770704456</v>
+        <v>1.0361348309112479</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0347081770704456</v>
+        <v>1.0361348309112479</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2030,28 +2030,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.63610000000006</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.079500489758036</v>
+        <v>21.078743736292193</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.9204995102419637</v>
+        <v>-3.9212562637078072</v>
       </c>
       <c r="G37" s="0">
-        <v>3.9204995102419637</v>
+        <v>3.9212562637078072</v>
       </c>
       <c r="H37" s="0">
-        <v>20.579500489758036</v>
+        <v>20.578743736292193</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.4204995102419637</v>
+        <v>-4.4212562637078072</v>
       </c>
       <c r="J37" s="0">
-        <v>4.4204995102419637</v>
+        <v>4.4212562637078072</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>598.2287</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.989298479721924</v>
+        <v>20.986483396296066</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9892984797219242</v>
+        <v>1.986483396296066</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9892984797219242</v>
+        <v>1.986483396296066</v>
       </c>
       <c r="H38" s="0">
-        <v>20.489298479721924</v>
+        <v>20.486483396296066</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4892984797219242</v>
+        <v>1.486483396296066</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4892984797219242</v>
+        <v>1.486483396296066</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2118,28 +2118,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>681.9153</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.851046904066745</v>
+        <v>20.841346856455072</v>
       </c>
       <c r="F39" s="0">
-        <v>1.8510469040667452</v>
+        <v>1.8413468564550719</v>
       </c>
       <c r="G39" s="0">
-        <v>1.8510469040667452</v>
+        <v>1.8413468564550719</v>
       </c>
       <c r="H39" s="0">
-        <v>20.351046904066745</v>
+        <v>20.341346856455072</v>
       </c>
       <c r="I39" s="0">
-        <v>1.3510469040667452</v>
+        <v>1.3413468564550719</v>
       </c>
       <c r="J39" s="0">
-        <v>1.3510469040667452</v>
+        <v>1.3413468564550719</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2162,28 +2162,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1171.8478</v>
+        <v>1170.2615000000001</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.239649784434693</v>
+        <v>21.238966874468794</v>
       </c>
       <c r="F40" s="0">
-        <v>0.2396497844346932</v>
+        <v>0.23896687446879383</v>
       </c>
       <c r="G40" s="0">
-        <v>0.2396497844346932</v>
+        <v>0.23896687446879383</v>
       </c>
       <c r="H40" s="0">
-        <v>20.739649784434693</v>
+        <v>20.738966874468794</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.2603502155653068</v>
+        <v>-0.26103312553120617</v>
       </c>
       <c r="J40" s="0">
-        <v>0.2603502155653068</v>
+        <v>0.26103312553120617</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2206,28 +2206,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>665.75360000000001</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.239323723502011</v>
+        <v>21.238640838516439</v>
       </c>
       <c r="F41" s="0">
-        <v>0.73932372350201092</v>
+        <v>0.73864083851643869</v>
       </c>
       <c r="G41" s="0">
-        <v>0.73932372350201092</v>
+        <v>0.73864083851643869</v>
       </c>
       <c r="H41" s="0">
-        <v>20.739323723502011</v>
+        <v>20.738640838516439</v>
       </c>
       <c r="I41" s="0">
-        <v>0.23932372350201092</v>
+        <v>0.23864083851643869</v>
       </c>
       <c r="J41" s="0">
-        <v>0.23932372350201092</v>
+        <v>0.23864083851643869</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2250,28 +2250,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>343.99220000000003</v>
+        <v>344.02600000000001</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.07949657476739</v>
+        <v>21.078739119392129</v>
       </c>
       <c r="F42" s="0">
-        <v>1.8294965747673899</v>
+        <v>1.8287391193921287</v>
       </c>
       <c r="G42" s="0">
-        <v>1.8294965747673899</v>
+        <v>1.8287391193921287</v>
       </c>
       <c r="H42" s="0">
-        <v>20.57949657476739</v>
+        <v>20.578739119392129</v>
       </c>
       <c r="I42" s="0">
-        <v>1.3294965747673899</v>
+        <v>1.3287391193921288</v>
       </c>
       <c r="J42" s="0">
-        <v>1.3294965747673899</v>
+        <v>1.3287391193921288</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2294,28 +2294,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>584.32039999999995</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.989266397443217</v>
+        <v>20.986443232274244</v>
       </c>
       <c r="F43" s="0">
-        <v>0.98926639744321676</v>
+        <v>0.9864432322742438</v>
       </c>
       <c r="G43" s="0">
-        <v>0.98926639744321676</v>
+        <v>0.9864432322742438</v>
       </c>
       <c r="H43" s="0">
-        <v>20.489266397443217</v>
+        <v>20.486443232274244</v>
       </c>
       <c r="I43" s="0">
-        <v>0.48926639744321676</v>
+        <v>0.4864432322742438</v>
       </c>
       <c r="J43" s="0">
-        <v>0.48926639744321676</v>
+        <v>0.4864432322742438</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2338,28 +2338,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>660.15719999999999</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.851428155346923</v>
+        <v>20.837674340618349</v>
       </c>
       <c r="F44" s="0">
-        <v>0.85142815534692318</v>
+        <v>0.83767434061834933</v>
       </c>
       <c r="G44" s="0">
-        <v>0.85142815534692318</v>
+        <v>0.83767434061834933</v>
       </c>
       <c r="H44" s="0">
-        <v>20.351428155346923</v>
+        <v>20.337674340618349</v>
       </c>
       <c r="I44" s="0">
-        <v>0.35142815534692318</v>
+        <v>0.33767434061834933</v>
       </c>
       <c r="J44" s="0">
-        <v>0.35142815534692318</v>
+        <v>0.33767434061834933</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2382,28 +2382,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>581.95590000000004</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.034702509417162</v>
+        <v>21.036125920061714</v>
       </c>
       <c r="F45" s="0">
-        <v>1.034702509417162</v>
+        <v>1.0361259200617141</v>
       </c>
       <c r="G45" s="0">
-        <v>1.034702509417162</v>
+        <v>1.0361259200617141</v>
       </c>
       <c r="H45" s="0">
-        <v>20.534702509417162</v>
+        <v>20.536125920061714</v>
       </c>
       <c r="I45" s="0">
-        <v>0.53470250941716202</v>
+        <v>0.53612592006171411</v>
       </c>
       <c r="J45" s="0">
-        <v>0.53470250941716202</v>
+        <v>0.53612592006171411</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2426,28 +2426,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1432.1427000000001</v>
+        <v>1450.9502</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.837927822793482</v>
+        <v>20.917818214448218</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.1620721772065181</v>
+        <v>-1.0821817855517821</v>
       </c>
       <c r="G46" s="0">
-        <v>1.1620721772065181</v>
+        <v>1.0821817855517821</v>
       </c>
       <c r="H46" s="0">
-        <v>20.337927822793482</v>
+        <v>20.417818214448218</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.6620721772065181</v>
+        <v>-1.5821817855517821</v>
       </c>
       <c r="J46" s="0">
-        <v>1.6620721772065181</v>
+        <v>1.5821817855517821</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2470,28 +2470,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1393.6792</v>
+        <v>1401.4597000000001</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.838599116644893</v>
+        <v>20.912647992750198</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.1614008833551068</v>
+        <v>-1.0873520072498018</v>
       </c>
       <c r="G47" s="0">
-        <v>1.1614008833551068</v>
+        <v>1.0873520072498018</v>
       </c>
       <c r="H47" s="0">
-        <v>20.338599116644893</v>
+        <v>20.412647992750198</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.6614008833551068</v>
+        <v>-1.5873520072498017</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6614008833551068</v>
+        <v>1.5873520072498017</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2514,28 +2514,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1418.9514999999999</v>
+        <v>1394.8155999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.035302130029937</v>
+        <v>21.036543198896368</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.9646978699700632</v>
+        <v>-1.9634568011036322</v>
       </c>
       <c r="G48" s="0">
-        <v>1.9646978699700632</v>
+        <v>1.9634568011036322</v>
       </c>
       <c r="H48" s="0">
-        <v>20.535302130029937</v>
+        <v>20.536543198896368</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.4646978699700632</v>
+        <v>-2.4634568011036322</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4646978699700632</v>
+        <v>2.4634568011036322</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2558,28 +2558,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1319.8444999999999</v>
+        <v>1329.1301000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.035231120257059</v>
+        <v>21.036509565895138</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.71476887974294101</v>
+        <v>-0.71349043410486246</v>
       </c>
       <c r="G49" s="0">
-        <v>0.71476887974294101</v>
+        <v>0.71349043410486246</v>
       </c>
       <c r="H49" s="0">
-        <v>20.535231120257059</v>
+        <v>20.536509565895138</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.214768879742941</v>
+        <v>-1.2134904341048625</v>
       </c>
       <c r="J49" s="0">
-        <v>1.214768879742941</v>
+        <v>1.2134904341048625</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2602,28 +2602,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1370.9471000000001</v>
+        <v>1378.3186000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>20.99108297774454</v>
+        <v>20.989699930823552</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.50891702225545998</v>
+        <v>-0.51030006917644855</v>
       </c>
       <c r="G50" s="0">
-        <v>0.50891702225545998</v>
+        <v>0.51030006917644855</v>
       </c>
       <c r="H50" s="0">
-        <v>20.49108297774454</v>
+        <v>20.489699930823552</v>
       </c>
       <c r="I50" s="0">
-        <v>-1.00891702225546</v>
+        <v>-1.0103000691764485</v>
       </c>
       <c r="J50" s="0">
-        <v>1.00891702225546</v>
+        <v>1.0103000691764485</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1230.9086</v>
+        <v>1221.2897</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.239687798628136</v>
+        <v>21.239000271741556</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0396877986281368</v>
+        <v>2.039000271741557</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0396877986281368</v>
+        <v>2.039000271741557</v>
       </c>
       <c r="H51" s="0">
-        <v>20.739687798628136</v>
+        <v>20.739000271741556</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5396877986281368</v>
+        <v>1.539000271741557</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5396877986281368</v>
+        <v>1.539000271741557</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2690,28 +2690,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1142.3658</v>
+        <v>1153.4326000000001</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.035103963583392</v>
+        <v>21.036419606116084</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5351039635833921</v>
+        <v>3.536419606116084</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5351039635833921</v>
+        <v>3.536419606116084</v>
       </c>
       <c r="H52" s="0">
-        <v>20.535103963583392</v>
+        <v>20.536419606116084</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0351039635833921</v>
+        <v>3.036419606116084</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0351039635833921</v>
+        <v>3.036419606116084</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2734,28 +2734,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1183.6578999999999</v>
+        <v>1196.1094000000001</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>21.079496240431325</v>
+        <v>21.078738797725475</v>
       </c>
       <c r="F53" s="0">
-        <v>2.6794962404313267</v>
+        <v>2.678738797725476</v>
       </c>
       <c r="G53" s="0">
-        <v>2.6794962404313267</v>
+        <v>2.678738797725476</v>
       </c>
       <c r="H53" s="0">
-        <v>20.579496240431325</v>
+        <v>20.578738797725475</v>
       </c>
       <c r="I53" s="0">
-        <v>2.1794962404313267</v>
+        <v>2.178738797725476</v>
       </c>
       <c r="J53" s="0">
-        <v>2.1794962404313267</v>
+        <v>2.178738797725476</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2778,28 +2778,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.7965999999999</v>
+        <v>1146.1387</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.990521132072416</v>
+        <v>20.988744238560944</v>
       </c>
       <c r="F54" s="0">
-        <v>1.9905211320724163</v>
+        <v>1.988744238560944</v>
       </c>
       <c r="G54" s="0">
-        <v>1.9905211320724163</v>
+        <v>1.988744238560944</v>
       </c>
       <c r="H54" s="0">
-        <v>20.490521132072416</v>
+        <v>20.488744238560944</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4905211320724163</v>
+        <v>1.488744238560944</v>
       </c>
       <c r="J54" s="0">
-        <v>1.4905211320724163</v>
+        <v>1.488744238560944</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2822,28 +2822,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.21460000000002</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>20.989303060746458</v>
+        <v>20.986544338003611</v>
       </c>
       <c r="F55" s="0">
-        <v>1.4893030607464581</v>
+        <v>1.4865443380036112</v>
       </c>
       <c r="G55" s="0">
-        <v>1.4893030607464581</v>
+        <v>1.4865443380036112</v>
       </c>
       <c r="H55" s="0">
-        <v>20.489303060746458</v>
+        <v>20.486544338003611</v>
       </c>
       <c r="I55" s="0">
-        <v>0.98930306074645813</v>
+        <v>0.98654433800361119</v>
       </c>
       <c r="J55" s="0">
-        <v>0.98930306074645813</v>
+        <v>0.98654433800361119</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2866,28 +2866,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>684.51480000000004</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.851001357713411</v>
+        <v>20.841554114357752</v>
       </c>
       <c r="F56" s="0">
-        <v>0.35100135771341101</v>
+        <v>0.34155411435775207</v>
       </c>
       <c r="G56" s="0">
-        <v>0.35100135771341101</v>
+        <v>0.34155411435775207</v>
       </c>
       <c r="H56" s="0">
-        <v>20.351001357713411</v>
+        <v>20.341554114357752</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.14899864228658899</v>
+        <v>-0.15844588564224793</v>
       </c>
       <c r="J56" s="0">
-        <v>0.14899864228658899</v>
+        <v>0.15844588564224793</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2910,28 +2910,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>632.78740000000005</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.03745914756411</v>
+        <v>21.037991070795577</v>
       </c>
       <c r="F57" s="0">
-        <v>0.037459147564110395</v>
+        <v>0.037991070795577286</v>
       </c>
       <c r="G57" s="0">
-        <v>0.037459147564110395</v>
+        <v>0.037991070795577286</v>
       </c>
       <c r="H57" s="0">
-        <v>20.53745914756411</v>
+        <v>20.537991070795577</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.4625408524358896</v>
+        <v>-0.46200892920442271</v>
       </c>
       <c r="J57" s="0">
-        <v>0.4625408524358896</v>
+        <v>0.46200892920442271</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2954,28 +2954,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1105.7334000000001</v>
+        <v>1095.0534</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.079504409413847</v>
+        <v>21.078747901630074</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.4204955905861532</v>
+        <v>-2.4212520983699264</v>
       </c>
       <c r="G58" s="0">
-        <v>2.4204955905861532</v>
+        <v>2.4212520983699264</v>
       </c>
       <c r="H58" s="0">
-        <v>20.579504409413847</v>
+        <v>20.578747901630074</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.9204955905861532</v>
+        <v>-2.9212520983699264</v>
       </c>
       <c r="J58" s="0">
-        <v>2.9204955905861532</v>
+        <v>2.9212520983699264</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -2998,28 +2998,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.27829999999995</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.241258287479297</v>
+        <v>21.240645114872546</v>
       </c>
       <c r="F59" s="0">
-        <v>0.74125828747929745</v>
+        <v>0.74064511487254592</v>
       </c>
       <c r="G59" s="0">
-        <v>0.74125828747929745</v>
+        <v>0.74064511487254592</v>
       </c>
       <c r="H59" s="0">
-        <v>20.741258287479297</v>
+        <v>20.740645114872546</v>
       </c>
       <c r="I59" s="0">
-        <v>0.24125828747929745</v>
+        <v>0.24064511487254592</v>
       </c>
       <c r="J59" s="0">
-        <v>0.24125828747929745</v>
+        <v>0.24064511487254592</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3042,28 +3042,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>655.14710000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.991905897319786</v>
+        <v>20.991172807343784</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.50809410268021438</v>
+        <v>-0.50882719265621645</v>
       </c>
       <c r="G60" s="0">
-        <v>0.50809410268021438</v>
+        <v>0.50882719265621645</v>
       </c>
       <c r="H60" s="0">
-        <v>20.491905897319786</v>
+        <v>20.491172807343784</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.0080941026802144</v>
+        <v>-1.0088271926562165</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0080941026802144</v>
+        <v>1.0088271926562165</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3086,28 +3086,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>642.19590000000005</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>21.079499641845601</v>
+        <v>21.078742680093836</v>
       </c>
       <c r="F61" s="0">
-        <v>1.0794996418456009</v>
+        <v>1.0787426800938356</v>
       </c>
       <c r="G61" s="0">
-        <v>1.0794996418456009</v>
+        <v>1.0787426800938356</v>
       </c>
       <c r="H61" s="0">
-        <v>20.579499641845601</v>
+        <v>20.578742680093836</v>
       </c>
       <c r="I61" s="0">
-        <v>0.57949964184560088</v>
+        <v>0.57874268009383556</v>
       </c>
       <c r="J61" s="0">
-        <v>0.57949964184560088</v>
+        <v>0.57874268009383556</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3130,28 +3130,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>671.02829999999995</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.079499938392061</v>
+        <v>21.078743176680316</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.9205000616079389</v>
+        <v>-1.9212568233196841</v>
       </c>
       <c r="G62" s="0">
-        <v>1.9205000616079389</v>
+        <v>1.9212568233196841</v>
       </c>
       <c r="H62" s="0">
-        <v>20.579499938392061</v>
+        <v>20.578743176680316</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.4205000616079389</v>
+        <v>-2.4212568233196841</v>
       </c>
       <c r="J62" s="0">
-        <v>2.4205000616079389</v>
+        <v>2.4212568233196841</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3174,28 +3174,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>658.74609999999996</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.028329228159898</v>
+        <v>21.174761688986251</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.47167077184010253</v>
+        <v>-0.32523831101374867</v>
       </c>
       <c r="G63" s="0">
-        <v>0.47167077184010253</v>
+        <v>0.32523831101374867</v>
       </c>
       <c r="H63" s="0">
-        <v>20.528329228159898</v>
+        <v>20.674761688986251</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.97167077184010253</v>
+        <v>-0.82523831101374867</v>
       </c>
       <c r="J63" s="0">
-        <v>0.97167077184010253</v>
+        <v>0.82523831101374867</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3218,28 +3218,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>418.81540000000001</v>
+        <v>427.42320000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.988884775856075</v>
+        <v>20.985793698306423</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.511115224143925</v>
+        <v>-1.5142063016935765</v>
       </c>
       <c r="G64" s="0">
-        <v>1.511115224143925</v>
+        <v>1.5142063016935765</v>
       </c>
       <c r="H64" s="0">
-        <v>20.488884775856075</v>
+        <v>20.485793698306423</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.011115224143925</v>
+        <v>-2.0142063016935765</v>
       </c>
       <c r="J64" s="0">
-        <v>2.011115224143925</v>
+        <v>2.0142063016935765</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3262,28 +3262,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>593.42259999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.241212079047436</v>
+        <v>21.240596614085753</v>
       </c>
       <c r="F65" s="0">
-        <v>1.9912120790474361</v>
+        <v>1.990596614085753</v>
       </c>
       <c r="G65" s="0">
-        <v>1.9912120790474361</v>
+        <v>1.990596614085753</v>
       </c>
       <c r="H65" s="0">
-        <v>20.741212079047436</v>
+        <v>20.740596614085753</v>
       </c>
       <c r="I65" s="0">
-        <v>1.4912120790474361</v>
+        <v>1.490596614085753</v>
       </c>
       <c r="J65" s="0">
-        <v>1.4912120790474361</v>
+        <v>1.490596614085753</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3306,28 +3306,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>709.44029999999998</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.034793825521714</v>
+        <v>21.036192669026399</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4652061744782863</v>
+        <v>-2.4638073309736015</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4652061744782863</v>
+        <v>2.4638073309736015</v>
       </c>
       <c r="H66" s="0">
-        <v>20.534793825521714</v>
+        <v>20.536192669026399</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9652061744782863</v>
+        <v>-2.9638073309736015</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9652061744782863</v>
+        <v>2.9638073309736015</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3350,28 +3350,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>625.83199999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.034733936940871</v>
+        <v>21.036156262285335</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.46526606305912921</v>
+        <v>-0.46384373771466514</v>
       </c>
       <c r="G67" s="0">
-        <v>0.46526606305912921</v>
+        <v>0.46384373771466514</v>
       </c>
       <c r="H67" s="0">
-        <v>20.534733936940871</v>
+        <v>20.536156262285335</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.96526606305912921</v>
+        <v>-0.96384373771466514</v>
       </c>
       <c r="J67" s="0">
-        <v>0.96526606305912921</v>
+        <v>0.96384373771466514</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3394,28 +3394,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>889.9828</v>
+        <v>892.07839999999999</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.03764347620605</v>
+        <v>21.0381160779569</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0376434762060498</v>
+        <v>2.0381160779569001</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0376434762060498</v>
+        <v>2.0381160779569001</v>
       </c>
       <c r="H68" s="0">
-        <v>20.53764347620605</v>
+        <v>20.5381160779569</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5376434762060498</v>
+        <v>1.5381160779569001</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5376434762060498</v>
+        <v>1.5381160779569001</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3476,16 +3476,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.476</v>
+        <v>1.4770000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.821</v>
+        <v>1.8200000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.049000000000000002</v>
+        <v>0.047</v>
       </c>
       <c r="E2" s="0">
-        <v>0.058999999999999997</v>
+        <v>0.072999999999999996</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3495,19 +3495,19 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.016</v>
+        <v>0.021000000000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="D3" s="0">
-        <v>0.016</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="E3" s="0">
-        <v>0.025999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="F3" s="0">
-        <v>1.1000000000000001</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="G3" s="0">
         <v>0.69999999999999996</v>
@@ -3529,18 +3529,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.4850000000000001</v>
+        <v>1.4830000000000001</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.441</v>
+        <v>-0.42699999999999999</v>
       </c>
       <c r="F5" s="0">
-        <v>38.700000000000003</v>
+        <v>39</v>
       </c>
       <c r="G5" s="0">
-        <v>44.299999999999997</v>
+        <v>44.799999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -3548,16 +3548,16 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.5569999999999999</v>
+        <v>1.556</v>
       </c>
       <c r="C6" s="0">
         <v>1.907</v>
       </c>
       <c r="D6" s="0">
-        <v>0.041000000000000002</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="E6" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="F6" s="0"/>
       <c r="G6" s="0"/>
@@ -3572,7 +3572,7 @@
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
       <c r="E7" s="0">
-        <v>-0.497</v>
+        <v>-0.498</v>
       </c>
       <c r="F7" s="0">
         <v>37.299999999999997</v>
@@ -3662,7 +3662,7 @@
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
     <col min="2" max="2" width="7.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
-    <col min="4" max="4" width="6.7109375" customWidth="true"/>
+    <col min="4" max="4" width="5.7109375" customWidth="true"/>
     <col min="5" max="5" width="6.7109375" customWidth="true"/>
   </cols>
   <sheetData>
@@ -3688,13 +3688,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>20.521599999999999</v>
+        <v>20.512599999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>0.64939999999999998</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="D2" s="0">
-        <v>31.603000000000002</v>
+        <v>31.510000000000002</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3711,10 +3711,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.52500000000000002</v>
+        <v>0.53800000000000003</v>
       </c>
       <c r="E3" s="0">
-        <v>0.60160000000000002</v>
+        <v>0.59219999999999995</v>
       </c>
     </row>
     <row r="4">
@@ -3725,13 +3725,13 @@
         <v>0.42609999999999998</v>
       </c>
       <c r="C4" s="0">
-        <v>0.45429999999999998</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="D4" s="0">
         <v>0.93799999999999995</v>
       </c>
       <c r="E4" s="0">
-        <v>0.3518</v>
+        <v>0.35149999999999998</v>
       </c>
     </row>
   </sheetData>
